--- a/SupplierDetails.xlsx
+++ b/SupplierDetails.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Excel\05_Datafiles_For_Faculty\Chapter 01\Task\Task 1.1\Input File\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\ADVANCED_EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE62EF5A-B292-40E2-9854-D3D45DB2F6F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ACAA12B-946B-4E55-B1D6-B4F68D39E04E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -645,16 +645,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -962,15 +962,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D36"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.6640625" style="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="44.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -984,35 +984,35 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>101</v>
+        <v>5</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>102</v>
+        <v>6</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>12</v>
       </c>
@@ -1026,457 +1026,457 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B22" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C22" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D22" s="5" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
+    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="B26" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B34" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C34" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D34" s="6" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B35" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C35" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D35" s="5" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="10" t="s">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B36" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C36" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D36" s="12" t="s">
         <v>143</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="B26" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="C26" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="D26" s="12" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="14" t="s">
-        <v>111</v>
-      </c>
-      <c r="B36" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="C36" s="16" t="s">
-        <v>133</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>134</v>
       </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D36">
-    <sortCondition ref="B2:B36"/>
+    <sortCondition ref="A2:A36"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -1486,7 +1486,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1495,7 +1495,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
